--- a/data/trans_camb/P1002-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P1002-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 6,62</t>
+          <t>-2,95; 6,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 6,54</t>
+          <t>-2,58; 6,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,81; -1,81</t>
+          <t>-9,17; -1,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,79; 17,43</t>
+          <t>6,13; 17,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,93; 17,33</t>
+          <t>6,19; 18,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,12; -1,28</t>
+          <t>-9,11; -1,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,9; 10,28</t>
+          <t>2,96; 10,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,85; 10,65</t>
+          <t>3,2; 10,9</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-7,75; -2,6</t>
+          <t>-7,75; -2,5</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-30,11; 137,17</t>
+          <t>-30,32; 120,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-33,33; 127,62</t>
+          <t>-30,85; 139,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-91,13; -31,09</t>
+          <t>-90,08; -21,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49,06; 297,04</t>
+          <t>54,56; 360,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>49,23; 321,53</t>
+          <t>52,9; 328,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-80,99; -9,98</t>
+          <t>-82,03; -20,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,43; 165,49</t>
+          <t>29,28; 167,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>30,1; 177,81</t>
+          <t>31,92; 176,51</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-81,88; -41,31</t>
+          <t>-80,85; -38,25</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 4,21</t>
+          <t>-3,05; 4,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,51; -1,95</t>
+          <t>-7,73; -2,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 3,3</t>
+          <t>-3,73; 2,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 4,34</t>
+          <t>-4,21; 4,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,51; -2,48</t>
+          <t>-10,48; -2,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 0,28</t>
+          <t>-7,61; -0,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 3,3</t>
+          <t>-2,38; 3,44</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,03; -3,12</t>
+          <t>-8,13; -3,12</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 0,41</t>
+          <t>-4,54; 0,34</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-34,27; 75,34</t>
+          <t>-33,03; 76,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-82,11; -30,94</t>
+          <t>-81,87; -33,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-41,63; 60,98</t>
+          <t>-41,74; 52,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-27,78; 34,58</t>
+          <t>-25,75; 38,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-61,88; -18,14</t>
+          <t>-62,44; -16,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-45,52; 2,32</t>
+          <t>-45,19; -0,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-20,19; 35,53</t>
+          <t>-19,37; 36,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-63,21; -29,99</t>
+          <t>-65,17; -33,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-38,07; 4,81</t>
+          <t>-36,88; 3,68</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,5; 7,52</t>
+          <t>1,87; 7,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 2,87</t>
+          <t>-0,96; 2,95</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,86; 7,25</t>
+          <t>1,97; 7,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,69; 11,97</t>
+          <t>4,1; 11,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 4,66</t>
+          <t>-1,18; 4,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 5,56</t>
+          <t>0,2; 5,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,76; 8,74</t>
+          <t>3,64; 8,72</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 3,19</t>
+          <t>-0,55; 3,17</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,75; 5,55</t>
+          <t>1,9; 5,74</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>41,9; 1980,65</t>
+          <t>-5,83; 1972,13</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-63,67; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>30,14; 2023,03</t>
+          <t>25,02; 1904,5</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>65,21; 600,42</t>
+          <t>77,96; 564,14</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-38,29; 237,33</t>
+          <t>-28,52; 237,76</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 251,66</t>
+          <t>-1,27; 303,95</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>105,5; 575,74</t>
+          <t>106,1; 593,11</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-23,77; 222,24</t>
+          <t>-22,0; 215,8</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>44,93; 364,13</t>
+          <t>43,57; 401,44</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,68; 7,53</t>
+          <t>1,75; 7,49</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,04; 10,16</t>
+          <t>3,98; 10,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,46; 7,59</t>
+          <t>1,51; 8,19</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8,28; 18,03</t>
+          <t>8,61; 18,62</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,43; 17,13</t>
+          <t>6,93; 16,9</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 6,72</t>
+          <t>-2,36; 6,89</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,29; 12,34</t>
+          <t>6,48; 12,23</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,72; 12,68</t>
+          <t>6,3; 12,43</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,79; 6,33</t>
+          <t>0,9; 6,51</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>30,44; 880,24</t>
+          <t>42,47; 856,01</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>120,46; 1291,57</t>
+          <t>100,62; 1216,85</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20,17; 907,27</t>
+          <t>21,84; 992,37</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>86,45; 351,36</t>
+          <t>85,53; 364,26</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>66,11; 332,18</t>
+          <t>77,19; 337,07</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-27,0; 127,15</t>
+          <t>-26,69; 123,64</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>113,36; 392,58</t>
+          <t>113,98; 368,25</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>111,29; 371,91</t>
+          <t>109,93; 378,62</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>13,88; 173,82</t>
+          <t>15,69; 187,01</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 2,71</t>
+          <t>-6,16; 2,22</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 2,29</t>
+          <t>-6,11; 1,89</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,03; 0,55</t>
+          <t>-7,17; 0,07</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,72; 17,61</t>
+          <t>5,84; 17,38</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 6,77</t>
+          <t>-2,77; 7,22</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 7,26</t>
+          <t>-0,91; 7,17</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,06; 8,81</t>
+          <t>1,22; 9,02</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 3,03</t>
+          <t>-3,09; 3,41</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 2,75</t>
+          <t>-2,6; 2,96</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-71,87; 75,93</t>
+          <t>-73,05; 64,39</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-72,81; 68,83</t>
+          <t>-72,68; 57,86</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-77,11; 33,33</t>
+          <t>-78,68; 15,28</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>54,79; 465,89</t>
+          <t>68,15; 492,21</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-40,53; 183,2</t>
+          <t>-34,82; 207,64</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-21,34; 187,4</t>
+          <t>-14,88; 198,98</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,47; 189,63</t>
+          <t>13,41; 201,37</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-38,99; 63,86</t>
+          <t>-41,58; 81,31</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-37,02; 64,12</t>
+          <t>-33,77; 74,59</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2,93; 9,17</t>
+          <t>2,55; 9,44</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>3,19; 10,53</t>
+          <t>3,25; 10,55</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1,58; 6,84</t>
+          <t>1,22; 6,42</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2,1; 11,36</t>
+          <t>2,98; 11,09</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,09; 13,9</t>
+          <t>4,55; 13,67</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 6,47</t>
+          <t>0,16; 6,45</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,54; 8,93</t>
+          <t>3,85; 8,82</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>4,8; 11,1</t>
+          <t>4,6; 10,66</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1,68; 5,65</t>
+          <t>1,52; 5,71</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>72,35; 1852,79</t>
+          <t>52,9; 1954,24</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>94,49; 1989,68</t>
+          <t>71,0; 2060,97</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>37,39; 1258,78</t>
+          <t>33,12; 1510,91</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>33,22; 531,04</t>
+          <t>37,67; 505,84</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>51,37; 639,01</t>
+          <t>68,13; 690,12</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-14,46; 275,2</t>
+          <t>-2,84; 313,38</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>81,23; 531,66</t>
+          <t>95,0; 532,81</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>122,38; 612,3</t>
+          <t>120,08; 623,67</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>44,02; 355,89</t>
+          <t>38,54; 375,94</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 1,67</t>
+          <t>-3,55; 1,37</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 3,97</t>
+          <t>-1,56; 3,64</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,06; 5,92</t>
+          <t>-0,14; 5,93</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 1,4</t>
+          <t>-4,96; 1,06</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 6,03</t>
+          <t>-0,67; 6,17</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 5,09</t>
+          <t>-6,32; 5,08</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 0,44</t>
+          <t>-3,35; 0,66</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 3,92</t>
+          <t>-0,45; 3,96</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 4,48</t>
+          <t>-1,8; 4,4</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-50,96; 45,48</t>
+          <t>-51,98; 38,61</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-25,62; 102,68</t>
+          <t>-25,56; 94,48</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 149,76</t>
+          <t>-4,88; 145,47</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-45,44; 19,95</t>
+          <t>-45,67; 15,4</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 77,4</t>
+          <t>-5,75; 78,23</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-49,08; 59,09</t>
+          <t>-50,84; 58,4</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-41,23; 7,39</t>
+          <t>-40,31; 10,62</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 60,33</t>
+          <t>-5,4; 63,68</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-23,7; 68,74</t>
+          <t>-21,06; 65,57</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 3,79</t>
+          <t>-2,03; 3,61</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-6,08; -1,18</t>
+          <t>-6,02; -1,28</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-7,14; -0,74</t>
+          <t>-6,8; -0,67</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2,84; 9,48</t>
+          <t>2,62; 9,42</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 0,42</t>
+          <t>-5,21; 0,5</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>3,04; 9,57</t>
+          <t>3,45; 9,74</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,33; 5,79</t>
+          <t>1,11; 5,78</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-4,76; -0,95</t>
+          <t>-4,93; -1,05</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 3,06</t>
+          <t>-3,1; 3,35</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-23,57; 63,11</t>
+          <t>-23,56; 58,03</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-64,41; -16,85</t>
+          <t>-65,09; -18,44</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-77,24; -11,13</t>
+          <t>-74,75; -9,88</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>25,59; 124,65</t>
+          <t>24,29; 124,77</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-48,4; 5,26</t>
+          <t>-48,91; 6,54</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>27,26; 124,35</t>
+          <t>31,12; 134,41</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>14,1; 79,35</t>
+          <t>11,56; 76,27</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-50,24; -12,15</t>
+          <t>-50,58; -13,62</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-39,02; 38,36</t>
+          <t>-31,3; 42,37</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,86</t>
+          <t>0,39; 2,73</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 1,29</t>
+          <t>-0,9; 1,22</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 1,46</t>
+          <t>-1,23; 1,43</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4,08; 7,06</t>
+          <t>4,07; 7,18</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,63</t>
+          <t>0,83; 3,68</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 2,84</t>
+          <t>-0,57; 2,98</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,63; 4,54</t>
+          <t>2,57; 4,57</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,06</t>
+          <t>0,27; 2,1</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 1,87</t>
+          <t>-0,3; 1,93</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>7,52; 61,43</t>
+          <t>7,03; 59,19</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-14,78; 28,6</t>
+          <t>-16,25; 26,26</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-19,51; 30,5</t>
+          <t>-21,92; 30,37</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>44,25; 89,79</t>
+          <t>44,12; 91,04</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>8,2; 45,48</t>
+          <t>9,56; 46,76</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 35,68</t>
+          <t>-6,1; 37,33</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>36,21; 71,56</t>
+          <t>35,0; 71,26</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>3,46; 31,8</t>
+          <t>3,55; 32,82</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 28,85</t>
+          <t>-3,94; 29,72</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P1002-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P1002-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-5,28</t>
+          <t>-5,57</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-5,01</t>
+          <t>-5,13</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-5,16</t>
+          <t>-5,35</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 6,01</t>
+          <t>-3,0; 6,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 6,75</t>
+          <t>-2,64; 6,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,17; -1,94</t>
+          <t>-9,86; -2,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,13; 17,94</t>
+          <t>5,62; 17,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,19; 18,08</t>
+          <t>5,75; 17,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,11; -1,57</t>
+          <t>-9,8; -1,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,96; 10,26</t>
+          <t>2,56; 10,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,2; 10,9</t>
+          <t>3,02; 10,59</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-7,75; -2,5</t>
+          <t>-8,03; -3,18</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-72,39%</t>
+          <t>-76,33%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-62,69%</t>
+          <t>-64,22%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-67,51%</t>
+          <t>-70,0%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-30,32; 120,15</t>
+          <t>-32,22; 130,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-30,85; 139,75</t>
+          <t>-28,6; 123,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-90,08; -21,62</t>
+          <t>-94,11; -48,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>54,56; 360,73</t>
+          <t>47,09; 313,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>52,9; 328,75</t>
+          <t>45,99; 312,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-82,03; -20,11</t>
+          <t>-82,43; -27,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,28; 167,53</t>
+          <t>24,59; 165,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>31,92; 176,51</t>
+          <t>31,51; 178,08</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-80,85; -38,25</t>
+          <t>-82,88; -50,04</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,37</t>
+          <t>-0,29</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-3,79</t>
+          <t>-4,09</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-2,13</t>
+          <t>-2,2</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 4,35</t>
+          <t>-2,97; 4,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,73; -2,01</t>
+          <t>-7,76; -2,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 2,93</t>
+          <t>-3,97; 3,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 4,92</t>
+          <t>-4,54; 4,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,48; -2,44</t>
+          <t>-10,61; -2,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,61; -0,05</t>
+          <t>-8,04; -0,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 3,44</t>
+          <t>-2,52; 3,26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,13; -3,12</t>
+          <t>-8,12; -3,25</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 0,34</t>
+          <t>-4,6; 0,63</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-5,07%</t>
+          <t>-3,95%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-25,93%</t>
+          <t>-28,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-19,36%</t>
+          <t>-20,08%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-33,03; 76,44</t>
+          <t>-35,27; 75,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-81,87; -33,45</t>
+          <t>-82,53; -36,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-41,74; 52,24</t>
+          <t>-42,07; 59,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-25,75; 38,49</t>
+          <t>-25,87; 38,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-62,44; -16,92</t>
+          <t>-64,38; -20,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-45,19; -0,46</t>
+          <t>-47,4; -1,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-19,37; 36,51</t>
+          <t>-20,01; 33,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-65,17; -33,13</t>
+          <t>-64,74; -31,71</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-36,88; 3,68</t>
+          <t>-36,9; 6,86</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4,41</t>
+          <t>4,78</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,09</t>
+          <t>3,24</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3,74</t>
+          <t>4,0</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,87; 7,57</t>
+          <t>1,42; 7,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 2,95</t>
+          <t>-1,26; 2,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,97; 7,31</t>
+          <t>2,19; 7,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,1; 11,9</t>
+          <t>3,68; 11,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 4,79</t>
+          <t>-1,34; 4,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,2; 5,8</t>
+          <t>0,54; 5,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,64; 8,72</t>
+          <t>3,54; 8,44</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 3,17</t>
+          <t>-0,7; 3,1</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,9; 5,74</t>
+          <t>1,99; 6,02</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>374,83%</t>
+          <t>405,97%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>161,63%</t>
+          <t>172,67%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 1972,13</t>
+          <t>19,92; 2131,24</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-63,67; —</t>
+          <t>-73,86; 862,57</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>25,02; 1904,5</t>
+          <t>38,22; 2138,4</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>77,96; 564,14</t>
+          <t>64,46; 503,11</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-28,52; 237,76</t>
+          <t>-34,07; 264,12</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 303,95</t>
+          <t>8,22; 307,02</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>106,1; 593,11</t>
+          <t>99,89; 573,65</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-22,0; 215,8</t>
+          <t>-27,87; 187,14</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>43,57; 401,44</t>
+          <t>55,47; 411,42</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4,22</t>
+          <t>3,93</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,1</t>
+          <t>4,45</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3,44</t>
+          <t>4,33</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,75; 7,49</t>
+          <t>1,76; 7,35</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,98; 10,34</t>
+          <t>3,9; 10,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,51; 8,19</t>
+          <t>1,2; 7,21</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8,61; 18,62</t>
+          <t>9,22; 18,89</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,93; 16,9</t>
+          <t>7,27; 16,7</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 6,89</t>
+          <t>0,41; 8,8</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,48; 12,23</t>
+          <t>6,36; 12,15</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,3; 12,43</t>
+          <t>6,38; 12,37</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,9; 6,51</t>
+          <t>1,9; 7,2</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>247,4%</t>
+          <t>230,44%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>64,35%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>42,47; 856,01</t>
+          <t>46,87; 1017,36</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>100,62; 1216,85</t>
+          <t>114,73; 1423,56</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21,84; 992,37</t>
+          <t>12,25; 958,74</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>85,53; 364,26</t>
+          <t>100,97; 344,56</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>77,19; 337,07</t>
+          <t>77,19; 330,37</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-26,69; 123,64</t>
+          <t>-0,13; 170,44</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>113,98; 368,25</t>
+          <t>118,84; 395,0</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>109,93; 378,62</t>
+          <t>113,44; 383,23</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>15,69; 187,01</t>
+          <t>31,67; 215,0</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-3,09</t>
+          <t>-3,39</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,08</t>
+          <t>2,32</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,22</t>
+          <t>-0,41</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 2,22</t>
+          <t>-5,96; 2,52</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 1,89</t>
+          <t>-6,44; 1,79</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 0,07</t>
+          <t>-7,54; -0,05</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,84; 17,38</t>
+          <t>5,61; 17,68</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 7,22</t>
+          <t>-3,32; 6,55</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 7,17</t>
+          <t>-1,79; 6,56</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,22; 9,02</t>
+          <t>1,05; 8,66</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 3,41</t>
+          <t>-2,99; 3,43</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 2,96</t>
+          <t>-3,11; 2,03</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-49,98%</t>
+          <t>-54,89%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>-6,74%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-73,05; 64,39</t>
+          <t>-72,13; 74,05</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-72,68; 57,86</t>
+          <t>-75,38; 55,18</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-78,68; 15,28</t>
+          <t>-81,7; 4,56</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>68,15; 492,21</t>
+          <t>56,87; 447,63</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-34,82; 207,64</t>
+          <t>-38,92; 183,96</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-14,88; 198,98</t>
+          <t>-22,1; 210,74</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,41; 201,37</t>
+          <t>10,53; 190,09</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-41,58; 81,31</t>
+          <t>-41,51; 74,56</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-33,77; 74,59</t>
+          <t>-40,0; 47,42</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3,94</t>
+          <t>3,83</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,33</t>
+          <t>3,2</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3,6</t>
+          <t>3,49</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2,55; 9,44</t>
+          <t>2,85; 9,61</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>3,25; 10,55</t>
+          <t>3,31; 10,68</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1,22; 6,42</t>
+          <t>1,46; 6,24</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2,98; 11,09</t>
+          <t>2,63; 10,94</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,55; 13,67</t>
+          <t>4,26; 14,06</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,16; 6,45</t>
+          <t>-0,2; 6,11</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,85; 8,82</t>
+          <t>3,67; 9,23</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>4,6; 10,66</t>
+          <t>4,84; 11,0</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1,52; 5,71</t>
+          <t>1,47; 5,51</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>295,05%</t>
+          <t>286,93%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>139,36%</t>
+          <t>135,23%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>52,9; 1954,24</t>
+          <t>69,39; 1924,7</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>71,0; 2060,97</t>
+          <t>101,06; 2297,24</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>33,12; 1510,91</t>
+          <t>34,99; 1318,72</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>37,67; 505,84</t>
+          <t>41,17; 489,69</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>68,13; 690,12</t>
+          <t>60,51; 600,87</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 313,38</t>
+          <t>-7,7; 277,4</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>95,0; 532,81</t>
+          <t>99,72; 550,43</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>120,08; 623,67</t>
+          <t>123,69; 667,18</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>38,54; 375,94</t>
+          <t>32,45; 337,17</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2,9</t>
+          <t>2,56</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,72</t>
+          <t>4,03</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1,93</t>
+          <t>3,36</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 1,37</t>
+          <t>-3,54; 1,3</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 3,64</t>
+          <t>-1,99; 3,69</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 5,93</t>
+          <t>-0,37; 5,67</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 1,06</t>
+          <t>-4,92; 1,05</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 6,17</t>
+          <t>-1,04; 5,95</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 5,08</t>
+          <t>0,79; 7,44</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 0,66</t>
+          <t>-3,41; 0,83</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 3,96</t>
+          <t>-0,43; 4,02</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 4,4</t>
+          <t>1,19; 5,42</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>56,42%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>45,89%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-51,98; 38,61</t>
+          <t>-54,32; 34,69</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-25,56; 94,48</t>
+          <t>-32,13; 90,79</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 145,47</t>
+          <t>-8,82; 143,53</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-45,67; 15,4</t>
+          <t>-44,77; 15,16</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 78,23</t>
+          <t>-10,34; 75,42</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-50,84; 58,4</t>
+          <t>6,01; 97,15</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-40,31; 10,62</t>
+          <t>-40,35; 12,79</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 63,68</t>
+          <t>-5,09; 65,94</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-21,06; 65,57</t>
+          <t>14,65; 85,24</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-3,4</t>
+          <t>-1,98</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>6,41</t>
+          <t>5,67</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,75</t>
+          <t>1,92</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 3,61</t>
+          <t>-2,09; 3,79</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-6,02; -1,28</t>
+          <t>-5,97; -1,14</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-6,8; -0,67</t>
+          <t>-4,53; 0,45</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2,62; 9,42</t>
+          <t>2,59; 9,1</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 0,5</t>
+          <t>-5,33; 0,54</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>3,45; 9,74</t>
+          <t>2,85; 8,67</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,11; 5,78</t>
+          <t>1,23; 5,86</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-4,93; -1,05</t>
+          <t>-4,78; -1,09</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 3,35</t>
+          <t>-0,32; 3,69</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-44,27%</t>
+          <t>-25,76%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>69,33%</t>
+          <t>61,34%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>22,63%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-23,56; 58,03</t>
+          <t>-22,12; 58,22</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-65,09; -18,44</t>
+          <t>-65,49; -17,84</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-74,75; -9,88</t>
+          <t>-51,0; 7,32</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>24,29; 124,77</t>
+          <t>23,59; 116,22</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-48,91; 6,54</t>
+          <t>-48,48; 7,8</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>31,12; 134,41</t>
+          <t>23,34; 109,81</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>11,56; 76,27</t>
+          <t>13,77; 79,56</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-50,58; -13,62</t>
+          <t>-49,52; -14,68</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-31,3; 42,37</t>
+          <t>-3,2; 49,46</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>0,23</t>
+          <t>0,54</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,49</t>
+          <t>2,3</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,9</t>
+          <t>1,47</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,73</t>
+          <t>0,36; 2,73</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 1,22</t>
+          <t>-0,92; 1,23</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 1,43</t>
+          <t>-0,63; 1,67</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4,07; 7,18</t>
+          <t>3,87; 6,87</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,68</t>
+          <t>0,63; 3,72</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 2,98</t>
+          <t>1,04; 3,46</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,57; 4,57</t>
+          <t>2,59; 4,51</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,1</t>
+          <t>0,3; 2,11</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 1,93</t>
+          <t>0,56; 2,31</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>21,35%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>7,03; 59,19</t>
+          <t>6,09; 58,56</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-16,25; 26,26</t>
+          <t>-16,37; 26,31</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-21,92; 30,37</t>
+          <t>-10,56; 36,01</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>44,12; 91,04</t>
+          <t>40,8; 87,43</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>9,56; 46,76</t>
+          <t>6,9; 47,83</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 37,33</t>
+          <t>11,53; 44,8</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>35,0; 71,26</t>
+          <t>35,23; 70,43</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>3,55; 32,82</t>
+          <t>4,04; 32,98</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 29,72</t>
+          <t>7,7; 36,07</t>
         </is>
       </c>
     </row>
